--- a/reports/telegram/aegis_daily_2026-08-12.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-12.xlsx
@@ -905,7 +905,7 @@
       </c>
       <c r="AU2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AU4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AU5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AU6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AU8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AU9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AU10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AU11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AU12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AU13" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AU14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AU15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AU16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AU17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AU18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="AU19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AU20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AU21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AU22" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AU23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="AU24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AU25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="AU26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AU27" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AU28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AU29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="AU30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="AU31" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="AU32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AU33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AU34" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AU35" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AU36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AU37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AU38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AU39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="AU40" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="AU41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AU42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:09</t>
+          <t>2026-08-12 03:26</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-12.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-12.xlsx
@@ -877,10 +877,10 @@
         <v>21.94</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>544.1</v>
+        <v>548.4</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AN2" s="3" t="n">
         <v>-1.66</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AU2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -1040,10 +1040,10 @@
         <v>27.92</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>2425.7</v>
+        <v>2445.7</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="AN3" s="3" t="n">
         <v>3.16</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -1199,10 +1199,10 @@
         <v>15</v>
       </c>
       <c r="AL4" s="5" t="n">
-        <v>11890</v>
+        <v>11896</v>
       </c>
       <c r="AM4" s="5" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="5" t="n">
         <v>7.36</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AU4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="V5" s="3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W5" s="3" t="inlineStr"/>
       <c r="X5" s="3" t="n">
@@ -1344,10 +1344,10 @@
         <v>12.02</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>1431.8</v>
+        <v>1429.6</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="AN5" s="3" t="n">
         <v>-0.62</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AU5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -1491,10 +1491,10 @@
         <v>7.86</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>1944.4</v>
+        <v>1942</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
         <v>-3.61</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AU6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -1642,10 +1642,10 @@
         <v>8.960000000000001</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>2300</v>
+        <v>2278.9</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="AN7" s="3" t="n">
         <v>-5.71</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="V8" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W8" s="3" t="inlineStr"/>
       <c r="X8" s="3" t="n">
@@ -1789,10 +1789,10 @@
         <v>12.5</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>1685</v>
+        <v>1685.8</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="3" t="n">
         <v>3.71</v>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AU8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       <c r="Q9" s="7" t="inlineStr"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 4→5 · Conf 71% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 4→5 · Conf 72% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr"/>
       <c r="T9" s="7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="V9" s="7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W9" s="7" t="inlineStr"/>
       <c r="X9" s="7" t="n">
@@ -1936,10 +1936,10 @@
         <v>13.14</v>
       </c>
       <c r="AL9" s="7" t="n">
-        <v>340.45</v>
+        <v>338.45</v>
       </c>
       <c r="AM9" s="7" t="n">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="AN9" s="7" t="n">
         <v>-2.1</v>
@@ -1964,14 +1964,14 @@
       </c>
       <c r="AU9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>BEL_IND_20260801</t>
+          <t>POWERGRID_IND_20260801</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Bharat Electronics</t>
+          <t>Power Grid</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -2010,10 +2010,10 @@
         <v>6</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M10" s="7" t="inlineStr"/>
       <c r="N10" s="7" t="inlineStr"/>
@@ -2022,12 +2022,16 @@
       <c r="Q10" s="7" t="inlineStr"/>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank ↑ 8→6 · Conf 66% · momentum → · 61d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr"/>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↑ 7→6 · Conf 68% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.3% ≤ -5.0% · exit</t>
+        </is>
+      </c>
       <c r="T10" s="7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="U10" s="7" t="inlineStr">
         <is>
@@ -2035,7 +2039,7 @@
         </is>
       </c>
       <c r="V10" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="W10" s="7" t="inlineStr"/>
       <c r="X10" s="7" t="n">
@@ -2053,43 +2057,43 @@
         </is>
       </c>
       <c r="AB10" s="7" t="n">
-        <v>405.9</v>
+        <v>268</v>
       </c>
       <c r="AC10" s="7" t="n">
-        <v>388.7</v>
+        <v>285.9</v>
       </c>
       <c r="AD10" s="7" t="n">
-        <v>393</v>
+        <v>261</v>
       </c>
       <c r="AE10" s="7" t="n">
-        <v>419</v>
+        <v>275</v>
       </c>
       <c r="AF10" s="7" t="n">
-        <v>385.605</v>
+        <v>254.6</v>
       </c>
       <c r="AG10" s="7" t="n">
-        <v>-0.8</v>
+        <v>-10.95</v>
       </c>
       <c r="AH10" s="7" t="n">
-        <v>438.372</v>
+        <v>289.44</v>
       </c>
       <c r="AI10" s="7" t="n">
-        <v>12.78</v>
+        <v>1.24</v>
       </c>
       <c r="AJ10" s="7" t="n">
-        <v>469.0580400000001</v>
+        <v>309.7008</v>
       </c>
       <c r="AK10" s="7" t="n">
-        <v>20.67</v>
+        <v>8.32</v>
       </c>
       <c r="AL10" s="7" t="n">
-        <v>404.35</v>
+        <v>267.95</v>
       </c>
       <c r="AM10" s="7" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="AN10" s="7" t="n">
-        <v>4.43</v>
+        <v>-6.26</v>
       </c>
       <c r="AO10" s="7" t="n">
         <v>0</v>
@@ -2100,25 +2104,25 @@
       <c r="AQ10" s="7" t="inlineStr"/>
       <c r="AR10" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="AS10" s="7" t="n">
         <v>5</v>
       </c>
       <c r="AT10" s="7" t="n">
-        <v>12.78</v>
+        <v>1.24</v>
       </c>
       <c r="AU10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>POWERGRID_IND_20260801</t>
+          <t>BEL_IND_20260801</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -2138,12 +2142,12 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Power Grid</t>
+          <t>Bharat Electronics</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -2157,10 +2161,10 @@
         <v>7</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="inlineStr"/>
@@ -2169,16 +2173,12 @@
       <c r="Q11" s="7" t="inlineStr"/>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank → 7→7 · Conf 68% · momentum → · 61d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-6.3% ≤ -5.0% · exit</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-2.9%) · Rank ↑ 8→7 · Conf 65% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr"/>
       <c r="T11" s="7" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="U11" s="7" t="inlineStr">
         <is>
@@ -2204,43 +2204,43 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>268</v>
+        <v>405.9</v>
       </c>
       <c r="AC11" s="7" t="n">
-        <v>285.9</v>
+        <v>388.7</v>
       </c>
       <c r="AD11" s="7" t="n">
-        <v>261</v>
+        <v>393</v>
       </c>
       <c r="AE11" s="7" t="n">
-        <v>275</v>
+        <v>418</v>
       </c>
       <c r="AF11" s="7" t="n">
-        <v>254.6</v>
+        <v>385.605</v>
       </c>
       <c r="AG11" s="7" t="n">
-        <v>-10.95</v>
+        <v>-0.8</v>
       </c>
       <c r="AH11" s="7" t="n">
-        <v>289.44</v>
+        <v>438.372</v>
       </c>
       <c r="AI11" s="7" t="n">
-        <v>1.24</v>
+        <v>12.78</v>
       </c>
       <c r="AJ11" s="7" t="n">
-        <v>309.7008</v>
+        <v>469.0580400000001</v>
       </c>
       <c r="AK11" s="7" t="n">
-        <v>8.32</v>
+        <v>20.67</v>
       </c>
       <c r="AL11" s="7" t="n">
-        <v>270.1</v>
+        <v>405.85</v>
       </c>
       <c r="AM11" s="7" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="AN11" s="7" t="n">
-        <v>-6.26</v>
+        <v>4.43</v>
       </c>
       <c r="AO11" s="7" t="n">
         <v>0</v>
@@ -2251,18 +2251,18 @@
       <c r="AQ11" s="7" t="inlineStr"/>
       <c r="AR11" s="7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="AS11" s="7" t="n">
         <v>5</v>
       </c>
       <c r="AT11" s="7" t="n">
-        <v>1.24</v>
+        <v>12.78</v>
       </c>
       <c r="AU11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="V12" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W12" s="7" t="inlineStr"/>
       <c r="X12" s="7" t="n">
@@ -2377,10 +2377,10 @@
         <v>5.9</v>
       </c>
       <c r="AL12" s="7" t="n">
-        <v>282.65</v>
+        <v>279</v>
       </c>
       <c r="AM12" s="7" t="n">
-        <v>-1.29</v>
+        <v>0</v>
       </c>
       <c r="AN12" s="7" t="n">
         <v>-1.38</v>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AU12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2463,12 @@
       <c r="Q13" s="5" t="inlineStr"/>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 7→9 · Conf 67% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 7→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr"/>
       <c r="T13" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U13" s="5" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="V13" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W13" s="5" t="inlineStr"/>
       <c r="X13" s="5" t="n">
@@ -2524,10 +2524,10 @@
         <v>20.39</v>
       </c>
       <c r="AL13" s="5" t="n">
-        <v>522.25</v>
+        <v>515.05</v>
       </c>
       <c r="AM13" s="5" t="n">
-        <v>-1.38</v>
+        <v>0</v>
       </c>
       <c r="AN13" s="5" t="n">
         <v>4.18</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AU13" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="V14" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="W14" s="7" t="inlineStr"/>
       <c r="X14" s="7" t="n">
@@ -2671,10 +2671,10 @@
         <v>15.93</v>
       </c>
       <c r="AL14" s="7" t="n">
-        <v>411</v>
+        <v>412.6</v>
       </c>
       <c r="AM14" s="7" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="AN14" s="7" t="n">
         <v>0.32</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AU14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="V15" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W15" s="7" t="inlineStr"/>
       <c r="X15" s="7" t="n">
@@ -2810,10 +2810,10 @@
         <v>15.54</v>
       </c>
       <c r="AL15" s="7" t="n">
-        <v>239.84</v>
+        <v>239.45</v>
       </c>
       <c r="AM15" s="7" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="AN15" s="7" t="n">
         <v>-0.02</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AU15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank #12 · Conf 65% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-3.0%) · Rank #12 · Conf 65% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr"/>
@@ -2921,10 +2921,10 @@
         <v>2064.89990234375</v>
       </c>
       <c r="AD16" s="5" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="AE16" s="5" t="n">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="AF16" s="5" t="n">
         <v>1961.655</v>
@@ -2945,10 +2945,10 @@
         <v>15.56</v>
       </c>
       <c r="AL16" s="5" t="n">
-        <v>2087.2</v>
+        <v>2064.9</v>
       </c>
       <c r="AM16" s="5" t="n">
-        <v>-1.07</v>
+        <v>0</v>
       </c>
       <c r="AN16" s="5" t="n">
         <v>0</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AU16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>15</v>
       </c>
       <c r="AL17" s="5" t="n">
-        <v>2300</v>
+        <v>2278.9</v>
       </c>
       <c r="AM17" s="5" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="AN17" s="5" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AU17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -3229,10 +3229,10 @@
         <v>15</v>
       </c>
       <c r="AL18" s="5" t="n">
-        <v>451.55</v>
+        <v>444.35</v>
       </c>
       <c r="AM18" s="5" t="n">
-        <v>-1.59</v>
+        <v>0</v>
       </c>
       <c r="AN18" s="5" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AU18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -3370,10 +3370,10 @@
         <v>15</v>
       </c>
       <c r="AL19" s="5" t="n">
-        <v>113.5</v>
+        <v>114.03</v>
       </c>
       <c r="AM19" s="5" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="AN19" s="5" t="n">
         <v>0</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="AU19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -3511,10 +3511,10 @@
         <v>15</v>
       </c>
       <c r="AL20" s="5" t="n">
-        <v>411</v>
+        <v>412.6</v>
       </c>
       <c r="AM20" s="5" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="AN20" s="5" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AU20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -3652,10 +3652,10 @@
         <v>15</v>
       </c>
       <c r="AL21" s="5" t="n">
-        <v>282.65</v>
+        <v>279</v>
       </c>
       <c r="AM21" s="5" t="n">
-        <v>-1.29</v>
+        <v>0</v>
       </c>
       <c r="AN21" s="5" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AU21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -3793,10 +3793,10 @@
         <v>15</v>
       </c>
       <c r="AL22" s="5" t="n">
-        <v>595.15</v>
+        <v>586.65</v>
       </c>
       <c r="AM22" s="5" t="n">
-        <v>-1.43</v>
+        <v>0</v>
       </c>
       <c r="AN22" s="5" t="n">
         <v>0</v>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AU22" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -3934,10 +3934,10 @@
         <v>15</v>
       </c>
       <c r="AL23" s="5" t="n">
-        <v>712.85</v>
+        <v>699.85</v>
       </c>
       <c r="AM23" s="5" t="n">
-        <v>-1.82</v>
+        <v>0</v>
       </c>
       <c r="AN23" s="5" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AU23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -4071,10 +4071,10 @@
         <v>15</v>
       </c>
       <c r="AL24" s="5" t="n">
-        <v>127.1</v>
+        <v>126.3</v>
       </c>
       <c r="AM24" s="5" t="n">
-        <v>-0.63</v>
+        <v>-0.24</v>
       </c>
       <c r="AN24" s="5" t="n">
         <v>0</v>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="AU24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -4208,10 +4208,10 @@
         <v>15</v>
       </c>
       <c r="AL25" s="5" t="n">
-        <v>5474</v>
+        <v>5536</v>
       </c>
       <c r="AM25" s="5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN25" s="5" t="n">
         <v>0</v>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AU25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -4345,10 +4345,10 @@
         <v>15</v>
       </c>
       <c r="AL26" s="5" t="n">
-        <v>11471</v>
+        <v>11550</v>
       </c>
       <c r="AM26" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN26" s="5" t="n">
         <v>0</v>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="AU26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -4482,10 +4482,10 @@
         <v>15</v>
       </c>
       <c r="AL27" s="5" t="n">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="AM27" s="5" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="AN27" s="5" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AU27" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -4615,10 +4615,10 @@
         <v>15</v>
       </c>
       <c r="AL28" s="5" t="n">
-        <v>382.7</v>
+        <v>388</v>
       </c>
       <c r="AM28" s="5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN28" s="5" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AU28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -4748,10 +4748,10 @@
         <v>15</v>
       </c>
       <c r="AL29" s="5" t="n">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="AM29" s="5" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="AN29" s="5" t="n">
         <v>0</v>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AU29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -4881,10 +4881,10 @@
         <v>15</v>
       </c>
       <c r="AL30" s="5" t="n">
-        <v>2772</v>
+        <v>2815</v>
       </c>
       <c r="AM30" s="5" t="n">
-        <v>1.55</v>
+        <v>-1.24</v>
       </c>
       <c r="AN30" s="5" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="AU30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -5022,10 +5022,10 @@
         <v>15</v>
       </c>
       <c r="AL31" s="5" t="n">
-        <v>1431.8</v>
+        <v>1429.6</v>
       </c>
       <c r="AM31" s="5" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="5" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="AU31" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -5163,10 +5163,10 @@
         <v>15</v>
       </c>
       <c r="AL32" s="5" t="n">
-        <v>1944.4</v>
+        <v>1942</v>
       </c>
       <c r="AM32" s="5" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="AN32" s="5" t="n">
         <v>0</v>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="AU32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -5304,10 +5304,10 @@
         <v>15</v>
       </c>
       <c r="AL33" s="5" t="n">
-        <v>2300</v>
+        <v>2278.9</v>
       </c>
       <c r="AM33" s="5" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="AN33" s="5" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AU33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -5445,10 +5445,10 @@
         <v>15</v>
       </c>
       <c r="AL34" s="5" t="n">
-        <v>1685</v>
+        <v>1685.8</v>
       </c>
       <c r="AM34" s="5" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AN34" s="5" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AU34" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -5586,10 +5586,10 @@
         <v>15</v>
       </c>
       <c r="AL35" s="5" t="n">
-        <v>340.45</v>
+        <v>338.45</v>
       </c>
       <c r="AM35" s="5" t="n">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="AN35" s="5" t="n">
         <v>0</v>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AU35" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -5727,10 +5727,10 @@
         <v>15</v>
       </c>
       <c r="AL36" s="5" t="n">
-        <v>390.75</v>
+        <v>393.5</v>
       </c>
       <c r="AM36" s="5" t="n">
-        <v>0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="AN36" s="5" t="n">
         <v>0</v>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AU36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -5868,10 +5868,10 @@
         <v>15</v>
       </c>
       <c r="AL37" s="5" t="n">
-        <v>270.1</v>
+        <v>267.95</v>
       </c>
       <c r="AM37" s="5" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="AN37" s="5" t="n">
         <v>0</v>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AU37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -6009,10 +6009,10 @@
         <v>15</v>
       </c>
       <c r="AL38" s="5" t="n">
-        <v>522.25</v>
+        <v>515.05</v>
       </c>
       <c r="AM38" s="5" t="n">
-        <v>-1.38</v>
+        <v>0</v>
       </c>
       <c r="AN38" s="5" t="n">
         <v>0</v>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AU38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -6150,10 +6150,10 @@
         <v>15</v>
       </c>
       <c r="AL39" s="5" t="n">
-        <v>404.35</v>
+        <v>405.85</v>
       </c>
       <c r="AM39" s="5" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="AN39" s="5" t="n">
         <v>0</v>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AU39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -6291,10 +6291,10 @@
         <v>15</v>
       </c>
       <c r="AL40" s="5" t="n">
-        <v>411</v>
+        <v>412.6</v>
       </c>
       <c r="AM40" s="5" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="AN40" s="5" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="AU40" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -6428,10 +6428,10 @@
         <v>15</v>
       </c>
       <c r="AL41" s="5" t="n">
-        <v>5510</v>
+        <v>5623.5</v>
       </c>
       <c r="AM41" s="5" t="n">
-        <v>2.06</v>
+        <v>-0.45</v>
       </c>
       <c r="AN41" s="5" t="n">
         <v>0</v>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="AU41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>
@@ -6569,10 +6569,10 @@
         <v>15</v>
       </c>
       <c r="AL42" s="5" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AM42" s="5" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="AN42" s="5" t="n">
         <v>0</v>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AU42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:26</t>
+          <t>2026-08-12 03:44</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-12.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-12.xlsx
@@ -905,7 +905,7 @@
       </c>
       <c r="AU2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AU4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AU5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AU6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AU8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AU9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AU10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AU11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AU12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AU13" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AU14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AU15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AU16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AU17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AU18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="AU19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AU20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AU21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AU22" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AU23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="AU24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AU25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="AU26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AU27" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AU28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AU29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="AU30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="AU31" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="AU32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AU33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AU34" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AU35" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AU36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AU37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AU38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AU39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="AU40" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="AU41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AU42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12 03:44</t>
+          <t>2026-08-12 04:27</t>
         </is>
       </c>
     </row>
